--- a/Dataset.xlsx
+++ b/Dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Semester 6\Visualisasi Informasi\Syntax\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kuliah\Semester 6\Visualisasi Informasi\Random Forest Digital Twin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2F6953-B7CD-4DEF-BF22-A012721B6FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57525D66-1EB4-4577-8C9D-8AD3FE13283D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0EAB97F0-0957-4D9B-B7FD-20E7CE86B6C9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="88">
   <si>
     <t>T1</t>
   </si>
@@ -289,78 +289,6 @@
   </si>
   <si>
     <t>7°20'31.304"</t>
-  </si>
-  <si>
-    <t>72.45</t>
-  </si>
-  <si>
-    <t>71.82</t>
-  </si>
-  <si>
-    <t>73.14</t>
-  </si>
-  <si>
-    <t>74.56</t>
-  </si>
-  <si>
-    <t>70.21</t>
-  </si>
-  <si>
-    <t>68.94</t>
-  </si>
-  <si>
-    <t>71.37</t>
-  </si>
-  <si>
-    <t>75.08</t>
-  </si>
-  <si>
-    <t>73.62</t>
-  </si>
-  <si>
-    <t>72.19</t>
-  </si>
-  <si>
-    <t>69.85</t>
-  </si>
-  <si>
-    <t>67.43</t>
-  </si>
-  <si>
-    <t>76.22</t>
-  </si>
-  <si>
-    <t>70.58</t>
-  </si>
-  <si>
-    <t>72.91</t>
-  </si>
-  <si>
-    <t>74.34</t>
-  </si>
-  <si>
-    <t>71.12</t>
-  </si>
-  <si>
-    <t>69.57</t>
-  </si>
-  <si>
-    <t>73.88</t>
-  </si>
-  <si>
-    <t>75.40</t>
-  </si>
-  <si>
-    <t>72.65</t>
-  </si>
-  <si>
-    <t>70.29</t>
-  </si>
-  <si>
-    <t>68.17</t>
-  </si>
-  <si>
-    <t>71.74</t>
   </si>
 </sst>
 </file>
@@ -853,8 +781,8 @@
       <c r="J2" s="4">
         <v>6.9</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>88</v>
+      <c r="K2" s="4">
+        <v>72.45</v>
       </c>
       <c r="L2" s="4">
         <v>23.1</v>
@@ -897,8 +825,8 @@
       <c r="J3" s="4">
         <v>6.7</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>89</v>
+      <c r="K3" s="4">
+        <v>71.819999999999993</v>
       </c>
       <c r="L3" s="4">
         <v>22.9</v>
@@ -941,8 +869,8 @@
       <c r="J4" s="4">
         <v>6.4</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>90</v>
+      <c r="K4" s="4">
+        <v>73.14</v>
       </c>
       <c r="L4" s="4">
         <v>23.4</v>
@@ -985,8 +913,8 @@
       <c r="J5" s="4">
         <v>6.3</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>91</v>
+      <c r="K5" s="4">
+        <v>74.56</v>
       </c>
       <c r="L5" s="4">
         <v>22.4</v>
@@ -1029,8 +957,8 @@
       <c r="J6" s="4">
         <v>6.4</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>92</v>
+      <c r="K6" s="4">
+        <v>70.209999999999994</v>
       </c>
       <c r="L6" s="4">
         <v>22.2</v>
@@ -1073,8 +1001,8 @@
       <c r="J7" s="4">
         <v>6.5</v>
       </c>
-      <c r="K7" s="4" t="s">
-        <v>93</v>
+      <c r="K7" s="4">
+        <v>68.94</v>
       </c>
       <c r="L7" s="4">
         <v>23.1</v>
@@ -1117,8 +1045,8 @@
       <c r="J8" s="4">
         <v>7</v>
       </c>
-      <c r="K8" s="4" t="s">
-        <v>94</v>
+      <c r="K8" s="4">
+        <v>71.37</v>
       </c>
       <c r="L8" s="4">
         <v>22.1</v>
@@ -1161,8 +1089,8 @@
       <c r="J9" s="4">
         <v>6.2</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>95</v>
+      <c r="K9" s="4">
+        <v>75.08</v>
       </c>
       <c r="L9" s="4">
         <v>22.7</v>
@@ -1205,8 +1133,8 @@
       <c r="J10" s="4">
         <v>6.4</v>
       </c>
-      <c r="K10" s="4" t="s">
-        <v>96</v>
+      <c r="K10" s="4">
+        <v>73.62</v>
       </c>
       <c r="L10" s="4">
         <v>23.7</v>
@@ -1249,8 +1177,8 @@
       <c r="J11" s="4">
         <v>6.5</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>97</v>
+      <c r="K11" s="4">
+        <v>72.19</v>
       </c>
       <c r="L11" s="4">
         <v>23.9</v>
@@ -1293,8 +1221,8 @@
       <c r="J12" s="4">
         <v>6.1</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>98</v>
+      <c r="K12" s="4">
+        <v>69.849999999999994</v>
       </c>
       <c r="L12" s="4">
         <v>23.4</v>
@@ -1337,8 +1265,8 @@
       <c r="J13" s="4">
         <v>6.2</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>99</v>
+      <c r="K13" s="4">
+        <v>67.430000000000007</v>
       </c>
       <c r="L13" s="4">
         <v>23.2</v>
@@ -1381,8 +1309,8 @@
       <c r="J14" s="4">
         <v>6</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>100</v>
+      <c r="K14" s="4">
+        <v>76.22</v>
       </c>
       <c r="L14" s="4">
         <v>22.9</v>
@@ -1425,8 +1353,8 @@
       <c r="J15" s="4">
         <v>6.3</v>
       </c>
-      <c r="K15" s="4" t="s">
-        <v>101</v>
+      <c r="K15" s="4">
+        <v>70.58</v>
       </c>
       <c r="L15" s="4">
         <v>22.5</v>
@@ -1469,8 +1397,8 @@
       <c r="J16" s="4">
         <v>7.5</v>
       </c>
-      <c r="K16" s="4" t="s">
-        <v>102</v>
+      <c r="K16" s="4">
+        <v>72.91</v>
       </c>
       <c r="L16" s="4">
         <v>22.9</v>
@@ -1513,8 +1441,8 @@
       <c r="J17" s="4">
         <v>7.4</v>
       </c>
-      <c r="K17" s="4" t="s">
-        <v>103</v>
+      <c r="K17" s="4">
+        <v>74.34</v>
       </c>
       <c r="L17" s="4">
         <v>22.6</v>
@@ -1557,8 +1485,8 @@
       <c r="J18" s="4">
         <v>6.9</v>
       </c>
-      <c r="K18" s="4" t="s">
-        <v>104</v>
+      <c r="K18" s="4">
+        <v>71.12</v>
       </c>
       <c r="L18" s="4">
         <v>23.6</v>
@@ -1601,8 +1529,8 @@
       <c r="J19" s="4">
         <v>5.9</v>
       </c>
-      <c r="K19" s="4" t="s">
-        <v>105</v>
+      <c r="K19" s="4">
+        <v>69.569999999999993</v>
       </c>
       <c r="L19" s="4">
         <v>23.1</v>
@@ -1645,8 +1573,8 @@
       <c r="J20" s="4">
         <v>7.2</v>
       </c>
-      <c r="K20" s="4" t="s">
-        <v>106</v>
+      <c r="K20" s="4">
+        <v>73.88</v>
       </c>
       <c r="L20" s="4">
         <v>23.4</v>
@@ -1689,8 +1617,8 @@
       <c r="J21" s="4">
         <v>5.9</v>
       </c>
-      <c r="K21" s="4" t="s">
-        <v>107</v>
+      <c r="K21" s="4">
+        <v>75.400000000000006</v>
       </c>
       <c r="L21" s="4">
         <v>22.3</v>
@@ -1733,8 +1661,8 @@
       <c r="J22" s="4">
         <v>6.7</v>
       </c>
-      <c r="K22" s="4" t="s">
-        <v>108</v>
+      <c r="K22" s="4">
+        <v>72.650000000000006</v>
       </c>
       <c r="L22" s="4">
         <v>23.9</v>
@@ -1777,8 +1705,8 @@
       <c r="J23" s="4">
         <v>6.2</v>
       </c>
-      <c r="K23" s="4" t="s">
-        <v>109</v>
+      <c r="K23" s="4">
+        <v>70.290000000000006</v>
       </c>
       <c r="L23" s="4">
         <v>23.5</v>
@@ -1821,8 +1749,8 @@
       <c r="J24" s="4">
         <v>6.3</v>
       </c>
-      <c r="K24" s="4" t="s">
-        <v>110</v>
+      <c r="K24" s="4">
+        <v>68.17</v>
       </c>
       <c r="L24" s="4">
         <v>22.9</v>
@@ -1865,8 +1793,8 @@
       <c r="J25" s="4">
         <v>5.8</v>
       </c>
-      <c r="K25" s="4" t="s">
-        <v>111</v>
+      <c r="K25" s="4">
+        <v>71.739999999999995</v>
       </c>
       <c r="L25" s="4">
         <v>23.6</v>
@@ -1876,15 +1804,33 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
+      <c r="D26" s="7">
+        <f>AVERAGE(D2:D25)</f>
+        <v>69.482083333333335</v>
+      </c>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7">
+        <f t="shared" ref="E26:L26" si="3">AVERAGE(F2:F25)</f>
+        <v>42.698333333333331</v>
+      </c>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7">
+        <f t="shared" si="3"/>
+        <v>78.358333333333334</v>
+      </c>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7">
+        <f t="shared" si="3"/>
+        <v>6.4875000000000007</v>
+      </c>
+      <c r="K26" s="7">
+        <f>AVERAGE(K2:K25)</f>
+        <v>71.98041666666667</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" si="3"/>
+        <v>23.054166666666671</v>
+      </c>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
@@ -1900,15 +1846,33 @@
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
+      <c r="D28" s="7">
+        <f>_xlfn.STDEV.S(D2:D25)</f>
+        <v>17.480273597293372</v>
+      </c>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7">
+        <f t="shared" ref="E28:L28" si="4">_xlfn.STDEV.S(F2:F25)</f>
+        <v>6.1317702009372121</v>
+      </c>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7">
+        <f t="shared" si="4"/>
+        <v>11.206478586908469</v>
+      </c>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7">
+        <f t="shared" si="4"/>
+        <v>0.46561086570318527</v>
+      </c>
+      <c r="K28" s="7">
+        <f t="shared" si="4"/>
+        <v>2.3283049986345579</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="4"/>
+        <v>0.52748720707064378</v>
+      </c>
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
